--- a/nr-add-more-examples/ig/CodeSystem-fr-core-cs-location-type-chambre.xlsx
+++ b/nr-add-more-examples/ig/CodeSystem-fr-core-cs-location-type-chambre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T09:52:49+00:00</t>
+    <t>2026-04-30T09:56:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-more-examples/ig/CodeSystem-fr-core-cs-location-type-chambre.xlsx
+++ b/nr-add-more-examples/ig/CodeSystem-fr-core-cs-location-type-chambre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T09:56:18+00:00</t>
+    <t>2026-04-30T12:26:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-more-examples/ig/CodeSystem-fr-core-cs-location-type-chambre.xlsx
+++ b/nr-add-more-examples/ig/CodeSystem-fr-core-cs-location-type-chambre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T12:26:28+00:00</t>
+    <t>2026-04-30T12:40:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-more-examples/ig/CodeSystem-fr-core-cs-location-type-chambre.xlsx
+++ b/nr-add-more-examples/ig/CodeSystem-fr-core-cs-location-type-chambre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T12:40:02+00:00</t>
+    <t>2026-04-30T12:42:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-more-examples/ig/CodeSystem-fr-core-cs-location-type-chambre.xlsx
+++ b/nr-add-more-examples/ig/CodeSystem-fr-core-cs-location-type-chambre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T12:42:30+00:00</t>
+    <t>2026-04-30T12:46:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-more-examples/ig/CodeSystem-fr-core-cs-location-type-chambre.xlsx
+++ b/nr-add-more-examples/ig/CodeSystem-fr-core-cs-location-type-chambre.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T12:46:16+00:00</t>
+    <t>2026-04-30T13:10:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -516,7 +516,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -528,7 +530,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -540,7 +544,9 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -552,7 +558,9 @@
       <c r="C5" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -564,7 +572,9 @@
       <c r="C6" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/nr-add-more-examples/ig/CodeSystem-fr-core-cs-location-type-chambre.xlsx
+++ b/nr-add-more-examples/ig/CodeSystem-fr-core-cs-location-type-chambre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T13:10:34+00:00</t>
+    <t>2026-04-30T13:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-more-examples/ig/CodeSystem-fr-core-cs-location-type-chambre.xlsx
+++ b/nr-add-more-examples/ig/CodeSystem-fr-core-cs-location-type-chambre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T13:20:47+00:00</t>
+    <t>2026-04-30T13:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
